--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EBAB5FB-BB94-9845-ACEB-E1554C24B569}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3941D32A-331B-2C42-9853-7199B9477746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
+    <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -11776,11 +11776,11 @@
         <v>6</v>
       </c>
       <c r="C384" s="7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D384" s="7">
         <f t="shared" si="30"/>
-        <v>0.87039999999999873</v>
+        <v>0.88039999999999874</v>
       </c>
       <c r="E384" s="1"/>
     </row>
@@ -11792,11 +11792,11 @@
         <v>5</v>
       </c>
       <c r="C385" s="7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D385" s="7">
         <f t="shared" si="30"/>
-        <v>0.88039999999999874</v>
+        <v>0.90039999999999876</v>
       </c>
       <c r="E385" s="1"/>
     </row>
@@ -11808,11 +11808,11 @@
         <v>4</v>
       </c>
       <c r="C386" s="7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D386" s="7">
         <f t="shared" si="30"/>
-        <v>0.89039999999999875</v>
+        <v>0.92039999999999877</v>
       </c>
       <c r="E386" s="1"/>
     </row>
@@ -11824,11 +11824,11 @@
         <v>3</v>
       </c>
       <c r="C387" s="7">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="D387" s="7">
         <f t="shared" si="30"/>
-        <v>0.90039999999999876</v>
+        <v>0.94039999999999879</v>
       </c>
       <c r="E387" s="1"/>
     </row>
@@ -11840,11 +11840,11 @@
         <v>2</v>
       </c>
       <c r="C388" s="7">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D388" s="7">
         <f t="shared" si="30"/>
-        <v>0.92539999999999878</v>
+        <v>0.96039999999999881</v>
       </c>
       <c r="E388" s="1"/>
     </row>
@@ -11856,11 +11856,11 @@
         <v>1</v>
       </c>
       <c r="C389" s="7">
-        <v>2.5000000000000001E-2</v>
+        <v>0.02</v>
       </c>
       <c r="D389" s="7">
         <f t="shared" si="30"/>
-        <v>0.9503999999999988</v>
+        <v>0.98039999999999883</v>
       </c>
       <c r="E389" s="1"/>
     </row>
@@ -11872,7 +11872,7 @@
         <v>0</v>
       </c>
       <c r="C390" s="7">
-        <v>0.05</v>
+        <v>0.02</v>
       </c>
       <c r="D390" s="7">
         <f>D389+C390</f>

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3941D32A-331B-2C42-9853-7199B9477746}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FBD3C4-32E0-8D4C-8389-09B40B7C2599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -11376,11 +11376,11 @@
         <v>23</v>
       </c>
       <c r="C367" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D367" s="7">
         <f t="shared" ref="D367:D389" si="30">D366+C367</f>
-        <v>0.777199999999999</v>
+        <v>0.77799999999999903</v>
       </c>
       <c r="E367" s="5">
         <v>46013</v>
@@ -11405,11 +11405,11 @@
         <v>22</v>
       </c>
       <c r="C368" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D368" s="7">
         <f t="shared" si="30"/>
-        <v>0.78039999999999898</v>
+        <v>0.78199999999999903</v>
       </c>
       <c r="E368" s="5">
         <v>46014</v>
@@ -11434,11 +11434,11 @@
         <v>21</v>
       </c>
       <c r="C369" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D369" s="7">
         <f t="shared" si="30"/>
-        <v>0.78359999999999896</v>
+        <v>0.78599999999999903</v>
       </c>
       <c r="E369" s="5">
         <v>46015</v>
@@ -11463,11 +11463,11 @@
         <v>20</v>
       </c>
       <c r="C370" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D370" s="7">
         <f t="shared" si="30"/>
-        <v>0.78679999999999894</v>
+        <v>0.78999999999999904</v>
       </c>
       <c r="E370" s="5">
         <v>46016</v>
@@ -11492,11 +11492,11 @@
         <v>19</v>
       </c>
       <c r="C371" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D371" s="7">
         <f t="shared" si="30"/>
-        <v>0.78999999999999893</v>
+        <v>0.79399999999999904</v>
       </c>
       <c r="E371" s="5">
         <v>46017</v>
@@ -11521,11 +11521,11 @@
         <v>18</v>
       </c>
       <c r="C372" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D372" s="7">
         <f t="shared" si="30"/>
-        <v>0.79319999999999891</v>
+        <v>0.79799999999999904</v>
       </c>
       <c r="E372" s="5">
         <v>46018</v>
@@ -11550,11 +11550,11 @@
         <v>17</v>
       </c>
       <c r="C373" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D373" s="7">
         <f t="shared" si="30"/>
-        <v>0.79639999999999889</v>
+        <v>0.80199999999999905</v>
       </c>
       <c r="E373" s="5">
         <v>46019</v>
@@ -11579,11 +11579,11 @@
         <v>16</v>
       </c>
       <c r="C374" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D374" s="7">
         <f t="shared" si="30"/>
-        <v>0.79959999999999887</v>
+        <v>0.80599999999999905</v>
       </c>
       <c r="E374" s="5">
         <v>46020</v>
@@ -11608,11 +11608,11 @@
         <v>15</v>
       </c>
       <c r="C375" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D375" s="7">
         <f t="shared" si="30"/>
-        <v>0.80279999999999885</v>
+        <v>0.80999999999999905</v>
       </c>
       <c r="E375" s="5">
         <v>46021</v>
@@ -11637,11 +11637,11 @@
         <v>14</v>
       </c>
       <c r="C376" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D376" s="7">
         <f t="shared" si="30"/>
-        <v>0.80599999999999883</v>
+        <v>0.81399999999999906</v>
       </c>
       <c r="E376" s="5">
         <v>46022</v>
@@ -11666,11 +11666,11 @@
         <v>13</v>
       </c>
       <c r="C377" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D377" s="7">
         <f t="shared" si="30"/>
-        <v>0.80919999999999881</v>
+        <v>0.81799999999999906</v>
       </c>
     </row>
     <row r="378" spans="1:8" x14ac:dyDescent="0.2">
@@ -11681,11 +11681,11 @@
         <v>12</v>
       </c>
       <c r="C378" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>4.0000000000000001E-3</v>
       </c>
       <c r="D378" s="7">
         <f t="shared" si="30"/>
-        <v>0.81239999999999879</v>
+        <v>0.82199999999999906</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.2">
@@ -11696,11 +11696,11 @@
         <v>11</v>
       </c>
       <c r="C379" s="7">
-        <v>3.2000000000000002E-3</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D379" s="7">
         <f t="shared" si="30"/>
-        <v>0.81559999999999877</v>
+        <v>0.83719999999999906</v>
       </c>
       <c r="E379" s="1"/>
     </row>
@@ -11712,11 +11712,11 @@
         <v>10</v>
       </c>
       <c r="C380" s="7">
-        <v>1.12E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D380" s="7">
         <f t="shared" si="30"/>
-        <v>0.82679999999999876</v>
+        <v>0.85239999999999905</v>
       </c>
       <c r="E380" s="6"/>
     </row>
@@ -11728,11 +11728,11 @@
         <v>9</v>
       </c>
       <c r="C381" s="7">
-        <v>1.12E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D381" s="7">
         <f t="shared" si="30"/>
-        <v>0.83799999999999875</v>
+        <v>0.86759999999999904</v>
       </c>
       <c r="E381" s="6"/>
     </row>
@@ -11744,11 +11744,11 @@
         <v>8</v>
       </c>
       <c r="C382" s="7">
-        <v>1.12E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D382" s="7">
         <f t="shared" si="30"/>
-        <v>0.84919999999999873</v>
+        <v>0.88279999999999903</v>
       </c>
       <c r="E382" s="1"/>
     </row>
@@ -11760,11 +11760,11 @@
         <v>7</v>
       </c>
       <c r="C383" s="7">
-        <v>1.12E-2</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D383" s="7">
         <f t="shared" si="30"/>
-        <v>0.86039999999999872</v>
+        <v>0.89799999999999902</v>
       </c>
       <c r="E383" s="1"/>
     </row>
@@ -11776,11 +11776,11 @@
         <v>6</v>
       </c>
       <c r="C384" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D384" s="7">
         <f t="shared" si="30"/>
-        <v>0.88039999999999874</v>
+        <v>0.91319999999999901</v>
       </c>
       <c r="E384" s="1"/>
     </row>
@@ -11792,11 +11792,11 @@
         <v>5</v>
       </c>
       <c r="C385" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D385" s="7">
         <f t="shared" si="30"/>
-        <v>0.90039999999999876</v>
+        <v>0.928399999999999</v>
       </c>
       <c r="E385" s="1"/>
     </row>
@@ -11808,11 +11808,11 @@
         <v>4</v>
       </c>
       <c r="C386" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D386" s="7">
         <f t="shared" si="30"/>
-        <v>0.92039999999999877</v>
+        <v>0.943599999999999</v>
       </c>
       <c r="E386" s="1"/>
     </row>
@@ -11824,11 +11824,11 @@
         <v>3</v>
       </c>
       <c r="C387" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D387" s="7">
         <f t="shared" si="30"/>
-        <v>0.94039999999999879</v>
+        <v>0.95879999999999899</v>
       </c>
       <c r="E387" s="1"/>
     </row>
@@ -11840,11 +11840,11 @@
         <v>2</v>
       </c>
       <c r="C388" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D388" s="7">
         <f t="shared" si="30"/>
-        <v>0.96039999999999881</v>
+        <v>0.97399999999999898</v>
       </c>
       <c r="E388" s="1"/>
     </row>
@@ -11856,11 +11856,11 @@
         <v>1</v>
       </c>
       <c r="C389" s="7">
-        <v>0.02</v>
+        <v>1.52E-2</v>
       </c>
       <c r="D389" s="7">
         <f t="shared" si="30"/>
-        <v>0.98039999999999883</v>
+        <v>0.98919999999999897</v>
       </c>
       <c r="E389" s="1"/>
     </row>
@@ -11872,11 +11872,11 @@
         <v>0</v>
       </c>
       <c r="C390" s="7">
-        <v>0.02</v>
+        <v>1.0999999999999999E-2</v>
       </c>
       <c r="D390" s="7">
         <f>D389+C390</f>
-        <v>1.0003999999999988</v>
+        <v>1.0001999999999989</v>
       </c>
       <c r="E390" s="1"/>
     </row>

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80FBD3C4-32E0-8D4C-8389-09B40B7C2599}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085A4E88-10AB-2E4C-A016-3432A5FDE77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4114,8 +4114,7 @@
         <v>89</v>
       </c>
       <c r="H116">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>100</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{085A4E88-10AB-2E4C-A016-3432A5FDE77A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571C3E04-D9C6-DD44-AD51-7E82D90679B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4142,8 +4142,7 @@
         <v>89</v>
       </c>
       <c r="H117">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{571C3E04-D9C6-DD44-AD51-7E82D90679B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78714287-B003-884E-9927-B9A7031C081F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4170,8 +4170,7 @@
         <v>89</v>
       </c>
       <c r="H118">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -4199,8 +4198,7 @@
         <v>89</v>
       </c>
       <c r="H119">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -4228,8 +4226,7 @@
         <v>89</v>
       </c>
       <c r="H120">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -4257,8 +4254,7 @@
         <v>89</v>
       </c>
       <c r="H121">
-        <f t="shared" si="9"/>
-        <v>160</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78714287-B003-884E-9927-B9A7031C081F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2DFA59-5DC4-F449-A97F-307739C993A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -3447,7 +3447,7 @@
         <v>79</v>
       </c>
       <c r="H93">
-        <f t="shared" ref="H93:H121" si="9">F93+$L$5</f>
+        <f t="shared" ref="H93:H115" si="9">F93+$L$5</f>
         <v>150</v>
       </c>
     </row>
@@ -4170,7 +4170,7 @@
         <v>89</v>
       </c>
       <c r="H118">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC2DFA59-5DC4-F449-A97F-307739C993A1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE735CC-9D94-5F4C-96BE-8681E872E582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4198,7 +4198,7 @@
         <v>89</v>
       </c>
       <c r="H119">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BEE735CC-9D94-5F4C-96BE-8681E872E582}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595A0C19-1A78-E444-917D-435D31805228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4198,7 +4198,7 @@
         <v>89</v>
       </c>
       <c r="H119">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{595A0C19-1A78-E444-917D-435D31805228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0422593-927C-564D-9519-BD0292FAC0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4226,7 +4226,7 @@
         <v>89</v>
       </c>
       <c r="H120">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -4254,7 +4254,7 @@
         <v>89</v>
       </c>
       <c r="H121">
-        <v>120</v>
+        <v>100</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0422593-927C-564D-9519-BD0292FAC0CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51881C4A-A4A4-4842-84A7-A34C7BBD679A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4226,7 +4226,7 @@
         <v>89</v>
       </c>
       <c r="H120">
-        <v>100</v>
+        <v>90</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51881C4A-A4A4-4842-84A7-A34C7BBD679A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CA606C-7BDE-6342-A33F-149BA872D9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4226,7 +4226,7 @@
         <v>89</v>
       </c>
       <c r="H120">
-        <v>90</v>
+        <v>80</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">

--- a/data_zed.xlsx
+++ b/data_zed.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/anastasioszafeiriou/Library/Mobile Documents/com~apple~CloudDocs/cronjobs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8CA606C-7BDE-6342-A33F-149BA872D9BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{214F8024-06E7-F149-B8B4-7BAD3B5560E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="700" windowWidth="29400" windowHeight="17120" xr2:uid="{1FD6CFA5-E782-3A43-9F72-F6518ACA9DFD}"/>
   </bookViews>
@@ -4254,7 +4254,7 @@
         <v>89</v>
       </c>
       <c r="H121">
-        <v>100</v>
+        <v>80</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
